--- a/Data/data_fusion_kg - Kimberly Sosa.xlsx
+++ b/Data/data_fusion_kg - Kimberly Sosa.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kmons\OneDrive\Escritorio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kmons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF6943E-633F-4336-994A-34DCC8634560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76171430-43A5-4D2B-AA8E-BEE1D1D4EE81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{193B4A23-EB6F-4B75-89B0-286228C2412B}"/>
+    <workbookView xWindow="10490" yWindow="1060" windowWidth="19200" windowHeight="12720" xr2:uid="{193B4A23-EB6F-4B75-89B0-286228C2412B}"/>
   </bookViews>
   <sheets>
     <sheet name="DOI" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <sheet name="Data" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -53,9 +52,6 @@
     <t>Publication Title</t>
   </si>
   <si>
-    <t>PublicationDate</t>
-  </si>
-  <si>
     <t>URL</t>
   </si>
   <si>
@@ -77,9 +73,6 @@
     <t>DataFusionClassificationReason</t>
   </si>
   <si>
-    <t>Method Name</t>
-  </si>
-  <si>
     <t>Method Key</t>
   </si>
   <si>
@@ -474,6 +467,12 @@
   </si>
   <si>
     <t>Southwest University, China</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>publication_date</t>
   </si>
 </sst>
 </file>
@@ -543,7 +542,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -558,10 +557,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -930,218 +926,218 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="87" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>30</v>
       </c>
       <c r="E2" s="4">
         <v>2021</v>
       </c>
       <c r="F2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="I2" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>40</v>
       </c>
       <c r="E3" s="4">
         <v>2021</v>
       </c>
       <c r="F3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="I3" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="K3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="E4" s="4">
         <v>2021</v>
       </c>
       <c r="F4" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="I4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="K4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="E5" s="4">
         <v>2021</v>
       </c>
       <c r="F5" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="I5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="K5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>67</v>
       </c>
       <c r="E6" s="4">
         <v>2021</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="I6" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="K6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
@@ -1167,122 +1163,122 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>143</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1313,227 +1309,227 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>107</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="J4" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="K4" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="L4" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="K5" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="L5" s="5" t="s">
         <v>134</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="I6" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="J6" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="K6" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>142</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>144</v>
       </c>
     </row>
   </sheetData>
